--- a/Evidence Handling/Dave Evidence/Evidence Handling Record - Dave.xlsx
+++ b/Evidence Handling/Dave Evidence/Evidence Handling Record - Dave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Evidence Handling/Dave Evidence/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{0AD82C83-FB65-4B68-B458-35F57E22243A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D75C2271-05B6-43D6-A01E-89515D017BCA}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{0AD82C83-FB65-4B68-B458-35F57E22243A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{076E3835-1BAA-42AF-A1D2-1FAB8FAF2243}"/>
   <bookViews>
-    <workbookView xWindow="-25770" yWindow="1200" windowWidth="21600" windowHeight="11385" xr2:uid="{4B523841-F448-4F74-9155-C94C48BB4A19}"/>
+    <workbookView xWindow="-28920" yWindow="165" windowWidth="29040" windowHeight="15840" xr2:uid="{4B523841-F448-4F74-9155-C94C48BB4A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
   <si>
     <t>Evidence / File Type</t>
   </si>
@@ -90,6 +90,21 @@
   </si>
   <si>
     <t>/home/pcadmin/Desktop/Artefacts/Evidence/TWO</t>
+  </si>
+  <si>
+    <t>f8a01fbe84ef960d7cbd793e0c52a6c9</t>
+  </si>
+  <si>
+    <t>evidence03.pcap</t>
+  </si>
+  <si>
+    <t>e_003</t>
+  </si>
+  <si>
+    <t>/home/bdsh/Desktop/Artefacts/Evidence/03 Pcap/</t>
+  </si>
+  <si>
+    <t>pcap</t>
   </si>
 </sst>
 </file>
@@ -475,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96D9203E-1CA1-4B1F-902E-282449A7789A}">
-  <dimension ref="B3:H5"/>
+  <dimension ref="B3:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" customWidth="1"/>
@@ -557,6 +572,29 @@
         <v>14</v>
       </c>
     </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
